--- a/input/mapping/073. OCB_GOLD_TCKH_T24_USER_BAOANH.xlsx
+++ b/input/mapping/073. OCB_GOLD_TCKH_T24_USER_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1748" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A0A16AF-6205-49BB-89BF-C27A174118DB}"/>
+  <xr:revisionPtr revIDLastSave="1754" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38E5D3EF-7D3E-4C99-9B14-8362E97F6801}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,50 +156,6 @@
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS T24_USER (
-    T_COMP_REPORT           STRING,
-    IP_ID                   STRING,
-    T_AUTHORISER            STRING,
-    T_DATE_TIME             STRING,
-    T_DEALER_DESK           STRING,
-    T_CLEAR_SCREEN          STRING,
-    T_PASSW_END_DATE        TIMESTAMP,
-    T_PASSW_CHANGE_DATE     TIMESTAMP,
-    T_DATE_LAST_SIGN_ON     TIMESTAMP,
-    T_ATTEMPTS_SINCE        DECIMAL(5, 0),
-    T_INPUT_DAY_MONTH       STRING,
-    T_FUNCTION_ID_LOG       STRING,
-    T_APPLICATION_LOG       STRING,
-    T_SECURITY_MGMT_L       STRING,
-    T_SIGN_ON_OFF_LOG       STRING,
-    T_DATA_FROM             STRING,
-    T_DATA_COMPARISON       STRING,
-    T_FIELD_NO              STRING,
-    T_FUNCTION              STRING,
-    T_VERSION               STRING,
-    T_APPLICATION           STRING,
-    T_COMPANY_RESTR         STRING,
-    T_ACCOUNT               STRING,
-    T_CUSTOMER              STRING,
-    T_INIT_APPLICATION      STRING,
-    T_ATTEMPTS              DECIMAL(2, 0),
-    T_TIME_OUT_MINUTES      DECIMAL(10, 0),
-    T_END_TIME              STRING,
-    T_START_TIME            STRING,
-    T_END_DATE_PROFILE      TIMESTAMP,
-    T_START_DATE_PROFILE    TIMESTAMP,
-    T_PASSWORD_VALIDITY     STRING,
-    T_DEPARTMENT_CODE       DECIMAL(4, 0),
-    T_COMPANY_CODE          STRING,
-    T_LANGUAGE              DECIMAL(2, 0),
-    T_CLASSIFICATION        STRING,
-    T_SIGN_ON_NAME          STRING,
-    T_USER_NAME             STRING,
-    DATA_DATE               STRING,
-    ID                      STRING,
-    MONTH_DAY               DECIMAL(4, 0)
-)
-USING DELTA;
 DELETE FROM T24_USER
 WHERE DATA_DATE = :DATADT;
 INSERT INTO T24_USER
